--- a/data/2025/02-arad/9262-arad/budget_file.xlsx
+++ b/data/2025/02-arad/9262-arad/budget_file.xlsx
@@ -504,37 +504,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>imprumuturi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>total_general</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>transferuri</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>bugetul_local</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>transferuri</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>fonduri_externe</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>inst_integral_venituri_proprii</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>total_general</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>inst_venituri_proprii_subventii</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>imprumuturi</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -620,23 +620,23 @@
         <v>1434276.03</v>
       </c>
       <c r="H4" s="3" t="n">
+        <v>57091</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1376806.03</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>57470</v>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n">
         <v>1301200.03</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>57470</v>
-      </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>1376806.03</v>
-      </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>75985</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>57091</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -663,23 +663,23 @@
         <v>1161962</v>
       </c>
       <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1109980</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>51982</v>
+      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n">
         <v>1090852</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>51982</v>
-      </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>1109980</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>71110</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -706,23 +706,23 @@
         <v>1186128</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1132796</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>53332</v>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n">
         <v>1113292</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>53332</v>
-      </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1132796</v>
-      </c>
-      <c r="M6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>72836</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         <v>1211169</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1156559</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>54610</v>
+      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n">
         <v>1136689</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>54610</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1156559</v>
-      </c>
-      <c r="M7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>74480</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -821,23 +821,23 @@
         <v>674796.03</v>
       </c>
       <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>674796.03</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n">
         <v>656281.03</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>674796.03</v>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>18515</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
         <v>761350</v>
       </c>
       <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>761350</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n">
         <v>742222</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>761350</v>
-      </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>19128</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -907,23 +907,23 @@
         <v>775108</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>775108</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n">
         <v>755604</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>775108</v>
-      </c>
-      <c r="M11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>19504</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -950,23 +950,23 @@
         <v>790285</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>790285</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n">
         <v>770415</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>790285</v>
-      </c>
-      <c r="M12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>19870</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
         <v>626341.03</v>
       </c>
       <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>626341.03</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="n"/>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n">
         <v>626341.03</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
@@ -1093,20 +1093,20 @@
         <v>681468</v>
       </c>
       <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>681468</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="n"/>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n">
         <v>681468</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>0</v>
@@ -1147,20 +1147,20 @@
         <v>693269</v>
       </c>
       <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
         <v>693269</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="n"/>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n">
         <v>693269</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>0</v>
@@ -1201,20 +1201,20 @@
         <v>706585</v>
       </c>
       <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
         <v>706585</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="n"/>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n">
         <v>706585</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N17" s="5" t="n">
         <v>0</v>
@@ -1293,13 +1293,13 @@
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="5" t="n"/>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n">
         <v>0</v>
       </c>
@@ -1347,13 +1347,13 @@
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="5" t="n"/>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n">
         <v>0</v>
       </c>
@@ -1401,13 +1401,13 @@
       <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="5" t="n"/>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n">
         <v>0</v>
       </c>
@@ -1453,13 +1453,13 @@
       <c r="I22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="7" t="n"/>
+      <c r="J22" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="K22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n">
         <v>0</v>
       </c>
@@ -1540,13 +1540,13 @@
       <c r="I24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="5" t="n"/>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="n">
         <v>0</v>
       </c>
@@ -1594,13 +1594,13 @@
       <c r="I25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="5" t="n"/>
+      <c r="J25" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L25" s="5" t="n"/>
       <c r="M25" s="5" t="n">
         <v>0</v>
       </c>
@@ -1648,13 +1648,13 @@
       <c r="I26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="5" t="n"/>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n">
         <v>0</v>
       </c>
@@ -1702,13 +1702,13 @@
       <c r="I27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="5" t="n"/>
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n">
         <v>0</v>
       </c>
@@ -1784,20 +1784,20 @@
         <v>326605</v>
       </c>
       <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="n">
         <v>326605</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5" t="n"/>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n">
         <v>326605</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
         <v>0</v>
@@ -1838,20 +1838,20 @@
         <v>334975</v>
       </c>
       <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
         <v>334975</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n"/>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n">
         <v>334975</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>0</v>
@@ -1892,20 +1892,20 @@
         <v>335324</v>
       </c>
       <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
         <v>335324</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5" t="n"/>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n">
         <v>335324</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N31" s="5" t="n">
         <v>0</v>
@@ -1946,20 +1946,20 @@
         <v>335607</v>
       </c>
       <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
         <v>335607</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n"/>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n">
         <v>335607</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>0</v>
@@ -2040,20 +2040,20 @@
         <v>8000</v>
       </c>
       <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="n"/>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n">
         <v>8000</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
@@ -2094,20 +2094,20 @@
         <v>10623</v>
       </c>
       <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
         <v>10623</v>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5" t="n"/>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n">
         <v>10623</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N35" s="5" t="n">
         <v>0</v>
@@ -2148,20 +2148,20 @@
         <v>1098</v>
       </c>
       <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
         <v>10899</v>
       </c>
-      <c r="I36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="n"/>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n">
         <v>10899</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
@@ -2239,11 +2239,11 @@
         <v>318605</v>
       </c>
       <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
         <v>318605</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" s="3" t="n">
         <v>0</v>
       </c>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>318605</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>0</v>
@@ -2279,11 +2279,11 @@
         <v>324352</v>
       </c>
       <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
         <v>324352</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
       </c>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
         <v>324352</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
@@ -2319,11 +2319,11 @@
         <v>324425</v>
       </c>
       <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
         <v>324425</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" s="3" t="n">
         <v>0</v>
       </c>
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>324425</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>0</v>
@@ -2362,11 +2362,11 @@
         <v>324445</v>
       </c>
       <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
         <v>324445</v>
       </c>
-      <c r="I42" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="7" t="n">
         <v>0</v>
       </c>
@@ -2374,12 +2374,12 @@
         <v>0</v>
       </c>
       <c r="L42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="n">
         <v>324445</v>
       </c>
-      <c r="M42" s="7" t="n"/>
-      <c r="N42" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" s="7" t="n"/>
       <c r="O42" s="6" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2466,52 +2466,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Alte impozite pe venit, profit și castiguri din capital</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column inst_integral_venituri_proprii</t>
         </is>
       </c>
     </row>
@@ -2646,58 +2646,56 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Impozite și taxe pe proprietate</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n">
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="7" t="n">
         <v>138170</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="n">
         <v>138170</v>
       </c>
-      <c r="I49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5" t="n">
+      <c r="J49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7" t="n">
         <v>138170</v>
       </c>
-      <c r="M49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="4" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'; duplicate of p2 with different values; cell re-read from image (unverified transcription)</t>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii; name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'; duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -2726,11 +2724,11 @@
         <v>172654</v>
       </c>
       <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
         <v>172654</v>
       </c>
-      <c r="I50" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
@@ -2738,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
         <v>172654</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>0</v>
@@ -2782,11 +2780,11 @@
         <v>179702.9</v>
       </c>
       <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="n">
         <v>179702.9</v>
       </c>
-      <c r="I51" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" s="5" t="n">
         <v>0</v>
       </c>
@@ -2794,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="5" t="n">
         <v>179702.9</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N51" s="5" t="n">
         <v>0</v>
@@ -2838,11 +2836,11 @@
         <v>188066.1</v>
       </c>
       <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
         <v>188066.1</v>
       </c>
-      <c r="I52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
@@ -2850,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
         <v>188066.1</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>0</v>
@@ -2934,11 +2932,11 @@
         <v>156406.03</v>
       </c>
       <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
         <v>156406.03</v>
       </c>
-      <c r="I54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
@@ -2946,11 +2944,11 @@
         <v>0</v>
       </c>
       <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
         <v>156406.03</v>
       </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" s="5" t="n">
         <v>0</v>
       </c>
@@ -2966,58 +2964,56 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>11.02</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Impozite si taxe pe bunuri si servicii</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n">
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="G55" s="7" t="n">
         <v>167716</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n">
         <v>167716</v>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="5" t="n">
+      <c r="J55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="7" t="n">
         <v>167716</v>
       </c>
-      <c r="M55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="4" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'; duplicate of p2 with different values; cell re-read from image (unverified transcription)</t>
+      <c r="N55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column imprumuturi; name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'; duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -3046,11 +3042,11 @@
         <v>171959.1</v>
       </c>
       <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
         <v>171959.1</v>
       </c>
-      <c r="I56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="5" t="n">
         <v>0</v>
       </c>
@@ -3058,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
         <v>171959.1</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>0</v>
@@ -3102,11 +3098,11 @@
         <v>176478.9</v>
       </c>
       <c r="H57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="n">
         <v>176478.9</v>
       </c>
-      <c r="I57" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" s="5" t="n">
         <v>0</v>
       </c>
@@ -3114,10 +3110,10 @@
         <v>0</v>
       </c>
       <c r="L57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="5" t="n">
         <v>176478.9</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N57" s="5" t="n">
         <v>0</v>
@@ -3198,11 +3194,11 @@
         <v>121471.03</v>
       </c>
       <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="n">
         <v>121471.03</v>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" s="5" t="n">
         <v>0</v>
       </c>
@@ -3210,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="5" t="n">
         <v>121471.03</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N59" s="5" t="n">
         <v>0</v>
@@ -3254,11 +3250,11 @@
         <v>126936</v>
       </c>
       <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
         <v>126936</v>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
       </c>
@@ -3266,11 +3262,11 @@
         <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
         <v>126936</v>
       </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N60" s="5" t="n">
         <v>0</v>
       </c>
@@ -3286,114 +3282,108 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>12.02</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Sume defalcate din TVA</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n">
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="7" t="n">
         <v>130218.1</v>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="7" t="n">
         <v>130218.1</v>
       </c>
-      <c r="I61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="5" t="n">
+      <c r="J61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n">
         <v>130218.1</v>
       </c>
-      <c r="M61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="4" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P61" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p2 with different values; cell re-read from image (unverified transcription)</t>
+      <c r="N61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column fonduri_externe; name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>12.02</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Sume defalcate din TVA</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n">
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n">
+      <c r="G62" s="7" t="n">
         <v>133800.9</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="7" t="n">
         <v>133800.9</v>
       </c>
-      <c r="I62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5" t="n">
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n">
         <v>133800.9</v>
       </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p2 with different values; cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
+      <c r="N62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column inst_integral_venituri_proprii; unparseable cell "00'0" in column fonduri_externe; name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -3472,52 +3462,52 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Alte impozite si taxe generale pe bunuri si servicii</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column imprumuturi</t>
         </is>
       </c>
     </row>
@@ -3659,11 +3649,11 @@
         <v>260</v>
       </c>
       <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J69" s="3" t="n">
         <v>0</v>
       </c>
@@ -3671,10 +3661,10 @@
         <v>0</v>
       </c>
       <c r="L69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3" t="n">
         <v>260</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>0</v>
@@ -3704,11 +3694,11 @@
         <v>275</v>
       </c>
       <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
       </c>
@@ -3716,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="n">
         <v>275</v>
-      </c>
-      <c r="M70" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -3749,11 +3739,11 @@
         <v>282</v>
       </c>
       <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
         <v>282</v>
       </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
       </c>
@@ -3761,11 +3751,11 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3" t="n">
         <v>282</v>
       </c>
-      <c r="M71" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N71" s="3" t="n">
         <v>0</v>
       </c>
@@ -3776,52 +3766,52 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Taxe pe servicii specifice</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" s="3" t="n">
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="7" t="n">
         <v>288</v>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="H72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7" t="n">
         <v>288</v>
       </c>
-      <c r="I72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="n">
+      <c r="J72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="7" t="n">
         <v>288</v>
       </c>
-      <c r="M72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="N72" s="7" t="n"/>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii</t>
         </is>
       </c>
     </row>
@@ -3890,11 +3880,11 @@
         <v>34675</v>
       </c>
       <c r="H74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="5" t="n">
         <v>34675</v>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" s="5" t="n">
         <v>0</v>
       </c>
@@ -3902,10 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
         <v>34675</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -3946,11 +3936,11 @@
         <v>40505</v>
       </c>
       <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n">
         <v>40505</v>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J75" s="5" t="n">
         <v>0</v>
       </c>
@@ -3958,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="5" t="n">
         <v>40505</v>
-      </c>
-      <c r="M75" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N75" s="5" t="n">
         <v>0</v>
@@ -4002,11 +3992,11 @@
         <v>41459</v>
       </c>
       <c r="H76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="5" t="n">
         <v>41459</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J76" s="5" t="n">
         <v>0</v>
       </c>
@@ -4014,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
         <v>41459</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
@@ -4058,11 +4048,11 @@
         <v>42390</v>
       </c>
       <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="n">
         <v>42390</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J77" s="5" t="n">
         <v>0</v>
       </c>
@@ -4070,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="L77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="5" t="n">
         <v>42390</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N77" s="5" t="n">
         <v>0</v>
@@ -4154,11 +4144,11 @@
         <v>5160</v>
       </c>
       <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="5" t="n">
         <v>5160</v>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J79" s="5" t="n">
         <v>0</v>
       </c>
@@ -4166,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="L79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="5" t="n">
         <v>5160</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N79" s="5" t="n">
         <v>0</v>
@@ -4210,11 +4200,11 @@
         <v>6123</v>
       </c>
       <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="n">
         <v>6123</v>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J80" s="5" t="n">
         <v>0</v>
       </c>
@@ -4222,10 +4212,10 @@
         <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="5" t="n">
         <v>6123</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N80" s="5" t="n">
         <v>0</v>
@@ -4266,11 +4256,11 @@
         <v>6283</v>
       </c>
       <c r="H81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="5" t="n">
         <v>6283</v>
       </c>
-      <c r="I81" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J81" s="5" t="n">
         <v>0</v>
       </c>
@@ -4278,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="5" t="n">
         <v>6283</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -4322,11 +4312,11 @@
         <v>6433</v>
       </c>
       <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="n">
         <v>6433</v>
       </c>
-      <c r="I82" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J82" s="5" t="n">
         <v>0</v>
       </c>
@@ -4334,10 +4324,10 @@
         <v>0</v>
       </c>
       <c r="L82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="5" t="n">
         <v>6433</v>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -4516,25 +4506,25 @@
         <v>143187</v>
       </c>
       <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>143187</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3" t="n">
         <v>123897</v>
       </c>
-      <c r="I88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>143187</v>
-      </c>
-      <c r="M88" s="3" t="n">
+      <c r="N88" s="3" t="n">
         <v>19290</v>
-      </c>
-      <c r="N88" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -4556,25 +4546,25 @@
         <v>160687</v>
       </c>
       <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>160687</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="n">
         <v>141282</v>
       </c>
-      <c r="I89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>160687</v>
-      </c>
-      <c r="M89" s="3" t="n">
+      <c r="N89" s="3" t="n">
         <v>19405</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -4596,25 +4586,25 @@
         <v>163425</v>
       </c>
       <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>163425</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3" t="n">
         <v>143557</v>
       </c>
-      <c r="I90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>163425</v>
-      </c>
-      <c r="M90" s="3" t="n">
+      <c r="N90" s="3" t="n">
         <v>19868</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -4636,25 +4626,25 @@
         <v>167744</v>
       </c>
       <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>167744</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="n">
         <v>147425</v>
       </c>
-      <c r="I91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>167744</v>
-      </c>
-      <c r="M91" s="3" t="n">
+      <c r="N91" s="3" t="n">
         <v>20319</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -4710,25 +4700,25 @@
         <v>258000.84</v>
       </c>
       <c r="H93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>258000.84</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3" t="n">
         <v>222329.84</v>
       </c>
-      <c r="I93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>258000.84</v>
-      </c>
-      <c r="M93" s="3" t="n">
+      <c r="N93" s="3" t="n">
         <v>35671</v>
-      </c>
-      <c r="N93" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -4755,25 +4745,25 @@
         <v>222398</v>
       </c>
       <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>222398</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="n">
         <v>187722</v>
       </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>222398</v>
-      </c>
-      <c r="M94" s="3" t="n">
+      <c r="N94" s="3" t="n">
         <v>34676</v>
-      </c>
-      <c r="N94" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -4800,25 +4790,25 @@
         <v>228294</v>
       </c>
       <c r="H95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>228294</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="3" t="n">
         <v>192798</v>
       </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>228294</v>
-      </c>
-      <c r="M95" s="3" t="n">
+      <c r="N95" s="3" t="n">
         <v>35496</v>
-      </c>
-      <c r="N95" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -4845,25 +4835,25 @@
         <v>233975</v>
       </c>
       <c r="H96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>233975</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3" t="n">
         <v>197706</v>
       </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>233975</v>
-      </c>
-      <c r="M96" s="3" t="n">
+      <c r="N96" s="3" t="n">
         <v>36269</v>
-      </c>
-      <c r="N96" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -4919,11 +4909,11 @@
         <v>22638</v>
       </c>
       <c r="H98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="3" t="n">
         <v>22638</v>
       </c>
-      <c r="I98" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J98" s="3" t="n">
         <v>0</v>
       </c>
@@ -4931,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="L98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3" t="n">
         <v>22638</v>
-      </c>
-      <c r="M98" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N98" s="3" t="n">
         <v>0</v>
@@ -4964,11 +4954,11 @@
         <v>20321</v>
       </c>
       <c r="H99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3" t="n">
         <v>20321</v>
       </c>
-      <c r="I99" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J99" s="3" t="n">
         <v>0</v>
       </c>
@@ -4976,10 +4966,10 @@
         <v>0</v>
       </c>
       <c r="L99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3" t="n">
         <v>20321</v>
-      </c>
-      <c r="M99" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>0</v>
@@ -5009,11 +4999,11 @@
         <v>16836</v>
       </c>
       <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
         <v>16836</v>
       </c>
-      <c r="I100" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
       </c>
@@ -5021,10 +5011,10 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="n">
         <v>16836</v>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -5054,11 +5044,11 @@
         <v>13387</v>
       </c>
       <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
         <v>13387</v>
       </c>
-      <c r="I101" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
       </c>
@@ -5066,10 +5056,10 @@
         <v>0</v>
       </c>
       <c r="L101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="n">
         <v>13387</v>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>0</v>
@@ -5130,20 +5120,20 @@
         <v>106201</v>
       </c>
       <c r="H103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="7" t="n">
         <v>106201</v>
       </c>
-      <c r="I103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="7" t="n"/>
+      <c r="J103" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="K103" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="7" t="n">
+      <c r="L103" s="7" t="n"/>
+      <c r="M103" s="7" t="n">
         <v>106201</v>
-      </c>
-      <c r="M103" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="N103" s="7" t="n">
         <v>0</v>
@@ -5178,11 +5168,11 @@
         <v>59876</v>
       </c>
       <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
         <v>59876</v>
       </c>
-      <c r="I104" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J104" s="3" t="n">
         <v>0</v>
       </c>
@@ -5190,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="L104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="3" t="n">
         <v>59876</v>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>0</v>
@@ -5293,11 +5283,11 @@
         <v>1000</v>
       </c>
       <c r="H107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="I107" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
       </c>
@@ -5305,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="5" t="n">
         <v>1000</v>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>0</v>
@@ -5557,22 +5547,22 @@
         <v>77470</v>
       </c>
       <c r="H112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>57470</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="5" t="n">
         <v>77470</v>
-      </c>
-      <c r="I112" s="5" t="n">
-        <v>57470</v>
-      </c>
-      <c r="J112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N112" s="5" t="n">
         <v>0</v>
@@ -5613,22 +5603,22 @@
         <v>65269</v>
       </c>
       <c r="H113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>13287</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>51982</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="5" t="n">
         <v>65269</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>51982</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v>13287</v>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N113" s="5" t="n">
         <v>0</v>
@@ -5669,22 +5659,22 @@
         <v>66967</v>
       </c>
       <c r="H114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>13635</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>53332</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="5" t="n">
         <v>66967</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>53332</v>
-      </c>
-      <c r="J114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v>13635</v>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N114" s="5" t="n">
         <v>0</v>
@@ -5738,25 +5728,25 @@
         <v>46333.71</v>
       </c>
       <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>46333.71</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="3" t="n">
         <v>26333.71</v>
       </c>
-      <c r="I116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="3" t="n">
-        <v>46333.71</v>
-      </c>
-      <c r="M116" s="3" t="n">
+      <c r="N116" s="3" t="n">
         <v>20000</v>
-      </c>
-      <c r="N116" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -5778,25 +5768,25 @@
         <v>46929</v>
       </c>
       <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>46929</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="3" t="n">
         <v>33539</v>
       </c>
-      <c r="I117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="3" t="n">
-        <v>46929</v>
-      </c>
-      <c r="M117" s="3" t="n">
+      <c r="N117" s="3" t="n">
         <v>13390</v>
-      </c>
-      <c r="N117" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -5893,25 +5883,25 @@
         <v>611551.76</v>
       </c>
       <c r="H120" s="5" t="n">
+        <v>57091</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>611551.76</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="5" t="n">
         <v>554460.76</v>
       </c>
-      <c r="I120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>611551.76</v>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N120" s="5" t="n">
-        <v>57091</v>
+        <v>0</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -5949,11 +5939,11 @@
         <v>374569</v>
       </c>
       <c r="H121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="7" t="n">
         <v>374569</v>
       </c>
-      <c r="I121" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="J121" s="7" t="n">
         <v>0</v>
       </c>
@@ -5961,12 +5951,12 @@
         <v>0</v>
       </c>
       <c r="L121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="7" t="n">
         <v>374569</v>
       </c>
-      <c r="M121" s="7" t="n"/>
-      <c r="N121" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" s="7" t="n"/>
       <c r="O121" s="6" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -6003,11 +5993,11 @@
         <v>384305</v>
       </c>
       <c r="H122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="5" t="n">
         <v>384305</v>
       </c>
-      <c r="I122" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J122" s="5" t="n">
         <v>0</v>
       </c>
@@ -6015,10 +6005,10 @@
         <v>0</v>
       </c>
       <c r="L122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="5" t="n">
         <v>384305</v>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N122" s="5" t="n">
         <v>0</v>
@@ -6059,20 +6049,20 @@
         <v>393528</v>
       </c>
       <c r="H123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="7" t="n">
         <v>393528</v>
       </c>
-      <c r="I123" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="7" t="n"/>
+      <c r="J123" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="K123" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L123" s="7" t="n">
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="7" t="n">
         <v>393528</v>
-      </c>
-      <c r="M123" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="N123" s="7" t="n">
         <v>0</v>
@@ -6153,11 +6143,11 @@
         <v>50461.32</v>
       </c>
       <c r="H125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="5" t="n">
         <v>50461.32</v>
       </c>
-      <c r="I125" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J125" s="5" t="n">
         <v>0</v>
       </c>
@@ -6165,10 +6155,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="5" t="n">
         <v>50461.32</v>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
         <v>0</v>
@@ -6209,20 +6199,20 @@
         <v>60731</v>
       </c>
       <c r="H126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="5" t="n">
         <v>60731</v>
       </c>
-      <c r="I126" s="5" t="n"/>
       <c r="J126" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K126" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K126" s="5" t="n"/>
       <c r="L126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="5" t="n">
         <v>60731</v>
-      </c>
-      <c r="M126" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N126" s="5" t="n">
         <v>0</v>
@@ -6263,11 +6253,11 @@
         <v>60912</v>
       </c>
       <c r="H127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5" t="n">
         <v>60912</v>
       </c>
-      <c r="I127" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J127" s="5" t="n">
         <v>0</v>
       </c>
@@ -6275,11 +6265,11 @@
         <v>0</v>
       </c>
       <c r="L127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="5" t="n">
         <v>60912</v>
       </c>
-      <c r="M127" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N127" s="5" t="n">
         <v>0</v>
       </c>
@@ -6295,58 +6285,56 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>34.02</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Asistenta sociala</t>
         </is>
       </c>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n">
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G128" s="5" t="n">
+      <c r="G128" s="7" t="n">
         <v>61081</v>
       </c>
-      <c r="H128" s="5" t="n">
+      <c r="H128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="7" t="n">
         <v>61081</v>
       </c>
-      <c r="I128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="5" t="n">
+      <c r="J128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="7" t="n"/>
+      <c r="L128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="7" t="n">
         <v>61081</v>
       </c>
-      <c r="M128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="P128" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'; duplicate of p4 with different values</t>
+      <c r="N128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column transferuri; name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'; duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -6439,25 +6427,25 @@
         <v>3642</v>
       </c>
       <c r="H131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>3642</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="5" t="n">
         <v>1843</v>
       </c>
-      <c r="I131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>3642</v>
-      </c>
-      <c r="M131" s="5" t="n">
+      <c r="N131" s="5" t="n">
         <v>1799</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -6495,25 +6483,25 @@
         <v>4794</v>
       </c>
       <c r="H132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>4794</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="5" t="n">
         <v>2941</v>
       </c>
-      <c r="I132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v>4794</v>
-      </c>
-      <c r="M132" s="5" t="n">
+      <c r="N132" s="5" t="n">
         <v>1853</v>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -6551,25 +6539,25 @@
         <v>4918</v>
       </c>
       <c r="H133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>4918</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="5" t="n">
         <v>3017</v>
       </c>
-      <c r="I133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v>4918</v>
-      </c>
-      <c r="M133" s="5" t="n">
+      <c r="N133" s="5" t="n">
         <v>1901</v>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -6607,25 +6595,25 @@
         <v>5037</v>
       </c>
       <c r="H134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>5037</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="5" t="n">
         <v>3090</v>
       </c>
-      <c r="I134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v>5037</v>
-      </c>
-      <c r="M134" s="5" t="n">
+      <c r="N134" s="5" t="n">
         <v>1947</v>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -6703,25 +6691,25 @@
         <v>123027</v>
       </c>
       <c r="H136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>123027</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="5" t="n">
         <v>121030</v>
       </c>
-      <c r="I136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>123027</v>
-      </c>
-      <c r="M136" s="5" t="n">
+      <c r="N136" s="5" t="n">
         <v>1997</v>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
@@ -6759,25 +6747,25 @@
         <v>106529</v>
       </c>
       <c r="H137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>106529</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="5" t="n">
         <v>104743</v>
       </c>
-      <c r="I137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v>106529</v>
-      </c>
-      <c r="M137" s="5" t="n">
+      <c r="N137" s="5" t="n">
         <v>1786</v>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
@@ -6815,25 +6803,25 @@
         <v>109318</v>
       </c>
       <c r="H138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>109318</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="5" t="n">
         <v>107486</v>
       </c>
-      <c r="I138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>109318</v>
-      </c>
-      <c r="M138" s="5" t="n">
+      <c r="N138" s="5" t="n">
         <v>1832</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
@@ -6871,25 +6859,25 @@
         <v>111918</v>
       </c>
       <c r="H139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>111918</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="5" t="n">
         <v>110042</v>
       </c>
-      <c r="I139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v>111918</v>
-      </c>
-      <c r="M139" s="5" t="n">
+      <c r="N139" s="5" t="n">
         <v>1876</v>
-      </c>
-      <c r="N139" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
@@ -6967,11 +6955,11 @@
         <v>26645</v>
       </c>
       <c r="H141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="5" t="n">
         <v>26645</v>
       </c>
-      <c r="I141" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J141" s="5" t="n">
         <v>0</v>
       </c>
@@ -6979,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="L141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="5" t="n">
         <v>26645</v>
-      </c>
-      <c r="M141" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N141" s="5" t="n">
         <v>0</v>
@@ -7023,11 +7011,11 @@
         <v>41090</v>
       </c>
       <c r="H142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="5" t="n">
         <v>41090</v>
       </c>
-      <c r="I142" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J142" s="5" t="n">
         <v>0</v>
       </c>
@@ -7035,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="L142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="5" t="n">
         <v>41090</v>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N142" s="5" t="n">
         <v>0</v>
@@ -7079,11 +7067,11 @@
         <v>41090</v>
       </c>
       <c r="H143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="5" t="n">
         <v>41090</v>
       </c>
-      <c r="I143" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J143" s="5" t="n">
         <v>0</v>
       </c>
@@ -7091,10 +7079,10 @@
         <v>0</v>
       </c>
       <c r="L143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="5" t="n">
         <v>41090</v>
-      </c>
-      <c r="M143" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N143" s="5" t="n">
         <v>0</v>
@@ -7135,11 +7123,11 @@
         <v>34911</v>
       </c>
       <c r="H144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="5" t="n">
         <v>34911</v>
       </c>
-      <c r="I144" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J144" s="5" t="n">
         <v>0</v>
       </c>
@@ -7147,10 +7135,10 @@
         <v>0</v>
       </c>
       <c r="L144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="5" t="n">
         <v>34911</v>
-      </c>
-      <c r="M144" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N144" s="5" t="n">
         <v>0</v>
@@ -7440,11 +7428,11 @@
         <v>26645</v>
       </c>
       <c r="H151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="5" t="n">
         <v>26645</v>
       </c>
-      <c r="I151" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J151" s="5" t="n">
         <v>0</v>
       </c>
@@ -7452,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="L151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="5" t="n">
         <v>26645</v>
-      </c>
-      <c r="M151" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N151" s="5" t="n">
         <v>0</v>
@@ -7496,11 +7484,11 @@
         <v>41090</v>
       </c>
       <c r="H152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="5" t="n">
         <v>41090</v>
       </c>
-      <c r="I152" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J152" s="5" t="n">
         <v>0</v>
       </c>
@@ -7508,10 +7496,10 @@
         <v>0</v>
       </c>
       <c r="L152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="5" t="n">
         <v>41090</v>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N152" s="5" t="n">
         <v>0</v>
@@ -7552,11 +7540,11 @@
         <v>41090</v>
       </c>
       <c r="H153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="5" t="n">
         <v>41090</v>
       </c>
-      <c r="I153" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J153" s="5" t="n">
         <v>0</v>
       </c>
@@ -7564,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="L153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="5" t="n">
         <v>41090</v>
-      </c>
-      <c r="M153" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N153" s="5" t="n">
         <v>0</v>
@@ -7608,11 +7596,11 @@
         <v>34911</v>
       </c>
       <c r="H154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="5" t="n">
         <v>34911</v>
       </c>
-      <c r="I154" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J154" s="5" t="n">
         <v>0</v>
       </c>
@@ -7620,10 +7608,10 @@
         <v>0</v>
       </c>
       <c r="L154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="5" t="n">
         <v>34911</v>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N154" s="5" t="n">
         <v>0</v>
@@ -7712,11 +7700,11 @@
         <v>-5012</v>
       </c>
       <c r="H156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="5" t="n">
         <v>-5012</v>
       </c>
-      <c r="I156" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J156" s="5" t="n">
         <v>0</v>
       </c>
@@ -7724,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="L156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="5" t="n">
         <v>-5012</v>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N156" s="5" t="n">
         <v>0</v>
@@ -7772,11 +7760,11 @@
         <v>-1231</v>
       </c>
       <c r="H157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="5" t="n">
         <v>-1231</v>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J157" s="5" t="n">
         <v>0</v>
       </c>
@@ -7784,10 +7772,10 @@
         <v>0</v>
       </c>
       <c r="L157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="5" t="n">
         <v>-1231</v>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
         <v>0</v>
@@ -7832,11 +7820,11 @@
         <v>-1262</v>
       </c>
       <c r="H158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="5" t="n">
         <v>-1262</v>
       </c>
-      <c r="I158" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J158" s="5" t="n">
         <v>0</v>
       </c>
@@ -7844,10 +7832,10 @@
         <v>0</v>
       </c>
       <c r="L158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="5" t="n">
         <v>-1262</v>
-      </c>
-      <c r="M158" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N158" s="5" t="n">
         <v>0</v>
@@ -7892,11 +7880,11 @@
         <v>-1292</v>
       </c>
       <c r="H159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="5" t="n">
         <v>-1292</v>
       </c>
-      <c r="I159" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J159" s="5" t="n">
         <v>0</v>
       </c>
@@ -7904,10 +7892,10 @@
         <v>0</v>
       </c>
       <c r="L159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="5" t="n">
         <v>-1292</v>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N159" s="5" t="n">
         <v>0</v>
@@ -8164,25 +8152,25 @@
         <v>-30869.6</v>
       </c>
       <c r="H165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>-30869.6</v>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="5" t="n">
         <v>-28097.6</v>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v>-30869.6</v>
-      </c>
-      <c r="M165" s="5" t="n">
+      <c r="N165" s="5" t="n">
         <v>-2772</v>
-      </c>
-      <c r="N165" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
@@ -8374,7 +8362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8420,60 +8408,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>03.02</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p1: 0 cells recovered</t>
+          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03.02</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p2: 8 cells recovered</t>
+          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>03.02</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p4: 0 cells recovered</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8523,14 +8526,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8548,14 +8551,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8573,14 +8576,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8598,14 +8601,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8623,7 +8626,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8646,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>03.02</t>
+          <t>04.02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8655,7 +8658,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8668,12 +8671,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>03.02</t>
+          <t>04.02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Venituri fiscale (rd.04+06+09+10+11+16)' vs 'Impozit pe venit'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8696,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>03.02</t>
+          <t>04.02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8708,22 +8711,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>04.02</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>unparseable cell "00'0" in column total</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8771,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>04.02</t>
+          <t>05.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8783,22 +8786,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>05.02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column total</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04.02</t>
+          <t>05.02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8868,7 +8871,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05.02</t>
+          <t>06.02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8893,7 +8896,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05.02</t>
+          <t>06.02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8918,7 +8921,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05.02</t>
+          <t>06.02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8955,7 +8958,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8968,19 +8971,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8993,12 +8996,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9021,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -9055,7 +9058,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9073,14 +9076,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9098,14 +9101,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9123,7 +9126,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
@@ -9133,54 +9136,54 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>07.02</t>
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>07.02</t>
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (45%): 'Impozitul pe veniturile din transferul p' vs 'Impozite si  taxe pe proprietate'</t>
+          <t>unparseable cell "00'0" in column inst_integral_venituri_proprii</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9189,16 +9192,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9233,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -9243,24 +9246,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>inst_integral_venituri_proprii</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9278,7 +9276,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -9335,12 +9333,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -9351,21 +9349,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>inst_venituri_proprii_subventii</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9383,14 +9376,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9408,14 +9401,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9433,14 +9426,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9453,12 +9446,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
@@ -9478,12 +9471,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Impozite și taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9496,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9515,25 +9508,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>11.02</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>imprumuturi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
+          <t>unparseable cell "00'0" in column imprumuturi</t>
         </is>
       </c>
     </row>
@@ -9640,12 +9633,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -9656,21 +9649,16 @@
           <t>11.02</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>imprumuturi</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9688,14 +9676,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9708,12 +9696,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -9733,12 +9721,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Impozite si taxe pe bunuri si servicii' vs 'Sume defalcate din TVA'</t>
+          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9746,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9795,7 +9783,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9813,7 +9801,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -9823,22 +9811,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>12.02</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>unparseable cell "00'0" in column fonduri_externe</t>
         </is>
       </c>
     </row>
@@ -9895,25 +9883,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>12.02</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>unparseable cell "00'0" in column inst_integral_venituri_proprii</t>
         </is>
       </c>
     </row>
@@ -9923,34 +9911,34 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>12.02</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>unparseable cell "00'0" in column fonduri_externe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -9961,21 +9949,16 @@
           <t>12.02</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>fonduri_externe</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9993,7 +9976,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Sume defalcate din TVA' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -10003,64 +9986,59 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>12.02</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>imprumuturi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>unparseable cell "00'0" in column imprumuturi</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>inst_integral_venituri_proprii</t>
+          <t>inst_venituri_proprii_subventii</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -10068,29 +10046,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>fonduri_externe</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -10098,29 +10071,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>imprumuturi</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -10128,17 +10096,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>inst_venituri_proprii_subventii</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10133,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10188,14 +10151,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10213,14 +10176,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10238,14 +10201,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10263,14 +10226,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10288,14 +10251,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10308,12 +10271,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -10333,12 +10296,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Taxe pe utilizarea bunurilor, autorizare' vs 'Taxe pe servicii specifice'</t>
+          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10321,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -10395,7 +10358,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10413,14 +10376,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10438,14 +10401,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10463,14 +10426,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10488,14 +10451,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10513,7 +10476,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -10523,47 +10486,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>16.02</t>
+        <v>3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>unparseable cell '1.065.632,00 1.036.982,00 1.015.574,00 1.320.485,63 1.211.169, 1.186.128,00 ,00' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>16.02</t>
+        <v>3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Alte impozite si taxe fiscale' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+          <t>unparseable cell '54.610,00 53.332,00 51.982,00 57.470,00 54.610,00 53.332,' in column est2027</t>
         </is>
       </c>
     </row>
@@ -10573,22 +10536,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>16.02</t>
+        <v>3</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>unparseable cell '1.011.022,00 983.650,00 963.592,00 1.263.015,63 1.156.559,00 1.132.796,00' in column est2027</t>
         </is>
       </c>
     </row>
@@ -10604,66 +10567,66 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>fonduri_externe</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>unparseable cell '1.065.632,00 1.036.982,00 1.015.574,00 1.320.485,63 1.211.169, 1.186.128,00 ,00' in column est2027</t>
+          <t>unparseable cell "00'0" in column fonduri_externe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>est2027</t>
+        <v>4</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>unparseable cell '54.610,00 53.332,00 51.982,00 57.470,00 54.610,00 53.332,' in column est2027</t>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>est2027</t>
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>unparseable cell '1.011.022,00 983.650,00 963.592,00 1.263.015,63 1.156.559,00 1.132.796,00' in column est2027</t>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
@@ -10673,22 +10636,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>4</v>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>fonduri_externe</t>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column fonduri_externe</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10683,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10738,14 +10701,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10763,14 +10726,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10788,14 +10751,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10813,14 +10776,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10838,14 +10801,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10858,12 +10821,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -10883,12 +10846,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10871,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -10945,7 +10908,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10963,14 +10926,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10988,14 +10951,14 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11013,14 +10976,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11033,12 +10996,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
         </is>
       </c>
     </row>
@@ -11058,12 +11021,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Transferuri intre unitati ale administra' vs 'Venituri din dobanzi'</t>
+          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
         </is>
       </c>
     </row>
@@ -11083,7 +11046,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -11095,25 +11058,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>4</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>83.02</t>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
+          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii</t>
         </is>
       </c>
     </row>
@@ -11170,32 +11133,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>4</v>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>inst_venituri_proprii_subventii</t>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column inst_venituri_proprii_subventii</t>
+          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11213,7 +11176,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -11223,22 +11186,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>4</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>83.02</t>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>unparseable cell "00'0" in column fonduri_externe</t>
         </is>
       </c>
     </row>
@@ -11295,25 +11258,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>4</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>fonduri_externe</t>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>34.02</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column fonduri_externe</t>
+          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
         </is>
       </c>
     </row>
@@ -11333,12 +11296,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Proiecte cu finantare din Fonduri extern' vs 'Agricultura, silvicultura, piscicultura '</t>
+          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11321,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -11395,7 +11358,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11413,14 +11376,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11438,14 +11401,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11463,7 +11426,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -11473,22 +11436,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>4</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>34.02</t>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>transferuri</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>unparseable cell '0,00 0,00' in column transferuri</t>
         </is>
       </c>
     </row>
@@ -11554,23 +11517,23 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Asistenta sociala' vs 'Venituri din taxe administrative, eliber'</t>
+          <t>name mismatch vs nomenclator (38%): 'Alte cheltuieli' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11579,23 +11542,23 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (38%): 'Alte cheltuieli' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11613,7 +11576,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Alte cheltuieli' vs 'Amenzi, penalitati si confiscari'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -11783,19 +11746,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Alte cheltuieli' vs 'Amenzi, penalitati si confiscari'</t>
+          <t>name mismatch vs nomenclator (32%): 'Cheltuieli de capital' vs 'Diverse venituri'</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11808,19 +11771,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'Cheltuieli de capital' vs 'Diverse venituri'</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11838,7 +11801,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Cheltuieli de capital' vs 'Diverse venituri'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -12008,19 +11971,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Cheltuieli de capital' vs 'Diverse venituri'</t>
+          <t>name mismatch vs nomenclator (28%): 'Operatiuni financiare (rd.38+39)' vs 'Transferuri voluntare,  altele decat sub'</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12033,19 +11996,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Operatiuni financiare (rd.38+39)' vs 'Transferuri voluntare,  altele decat sub'</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12063,7 +12026,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Operatiuni financiare (rd.38+39)' vs 'Transferuri voluntare,  altele decat sub'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -12233,19 +12196,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Operatiuni financiare (rd.38+39)' vs 'Transferuri voluntare,  altele decat sub'</t>
+          <t>name mismatch vs nomenclator (38%): 'Rambursari de credite externe si interne' vs 'Venituri din valorificarea unor bunuri'</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12258,19 +12221,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (38%): 'Rambursari de credite externe si interne' vs 'Venituri din valorificarea unor bunuri'</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12288,7 +12251,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Rambursari de credite externe si interne' vs 'Venituri din valorificarea unor bunuri'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -12458,19 +12421,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Rambursari de credite externe si interne' vs 'Venituri din valorificarea unor bunuri'</t>
+          <t>name mismatch vs nomenclator (30%): 'Plăți efectuate în anii precedenți și re' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12483,19 +12446,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (30%): 'Plăți efectuate în anii precedenți și re' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12513,7 +12476,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Plăți efectuate în anii precedenți și re' vs 'TITLUL IV SUBVENTII'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -12683,19 +12646,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Plăți efectuate în anii precedenți și re' vs 'TITLUL IV SUBVENTII'</t>
+          <t>name mismatch vs nomenclator (24%): 'Rezerve' vs 'Alte operaţiuni financiare'</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12708,19 +12671,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (24%): 'Rezerve' vs 'Alte operaţiuni financiare'</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12738,7 +12701,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Rezerve' vs 'Alte operaţiuni financiare'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -12808,19 +12771,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Rezerve' vs 'Alte operaţiuni financiare'</t>
+          <t>name mismatch vs nomenclator (25%): 'EXCEDENT (+) / DEFICIT (-) 1) (rd.01-rd.' vs 'Subventii de la bugetul de stat'</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12833,19 +12796,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (25%): 'EXCEDENT (+) / DEFICIT (-) 1) (rd.01-rd.' vs 'Subventii de la bugetul de stat'</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12863,7 +12826,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'EXCEDENT (+) / DEFICIT (-) 1) (rd.01-rd.' vs 'Subventii de la bugetul de stat'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -13012,56 +12975,6 @@
         </is>
       </c>
       <c r="F184" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>5</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (25%): 'EXCEDENT (+) / DEFICIT (-) 1) (rd.01-rd.' vs 'Subventii de la bugetul de stat'</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>5</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
@@ -13078,7 +12991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13100,7 +13013,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -13110,72 +13023,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>101</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1c1818617934c8125a976af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7d679ffe8608a91ea9a3db1bb7684f70a4532584e80f491871b2c6723ddc22b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL GENERAL AL MUNICIPIULUI ARAD PE ANUL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>general, pag. 1-5, 167 linii</t>
         </is>
